--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{543921AA-666F-4FEA-94FC-51405D51797E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EF65330-1F84-4E04-8654-11894B0ACE6E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26A3E96F-1F10-4E29-803C-F03093C5C411}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A4EB9EF-C00E-4BDA-89BF-2EB76D770547}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81B15C2B-1310-4914-BCB9-136BC1AAA495}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFB3200A-D7EA-4AFD-B55C-78D5A77E5595}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EF65330-1F84-4E04-8654-11894B0ACE6E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80502328-A601-4F75-AC3E-5AC6BB4A8B50}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A4EB9EF-C00E-4BDA-89BF-2EB76D770547}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3688C322-EC1C-483A-8038-A3A32FAF6A59}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFB3200A-D7EA-4AFD-B55C-78D5A77E5595}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{184ABA16-35A0-4953-9DAC-7DED626C41D0}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80502328-A601-4F75-AC3E-5AC6BB4A8B50}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6CE4A43-2076-45E6-A373-9E014D0E03F0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3688C322-EC1C-483A-8038-A3A32FAF6A59}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE7D6F76-4DA8-436C-9C46-5A532A9A6635}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{184ABA16-35A0-4953-9DAC-7DED626C41D0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B5C0A3-C1B3-4A14-B0EF-8DDD8BF48DDC}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6CE4A43-2076-45E6-A373-9E014D0E03F0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A461B228-DAB9-416C-B3B5-C43503FF87DC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE7D6F76-4DA8-436C-9C46-5A532A9A6635}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81298886-50E0-4034-92EF-1331FECE4BAD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B5C0A3-C1B3-4A14-B0EF-8DDD8BF48DDC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35F3B288-0D18-425A-A663-9B0A1EDB33E4}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -3427,13 +3427,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E6EC724-BEDC-4761-BF52-804921E258D0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A38BF3F5-8139-40B2-AC4D-BA6F3D6D1B1B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D26C8B89-6C3F-47D3-A123-192B001DD42E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F38F56BD-949C-4B0B-9D43-F42D92077E6F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{629427B6-BDB4-477E-B31A-23BEE583A1B7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{242600EC-3DC6-4B18-B5AC-906E18FE43F7}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -3427,13 +3427,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A38BF3F5-8139-40B2-AC4D-BA6F3D6D1B1B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA4CB56B-81C4-4C93-B38D-C479B7F1BA14}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F38F56BD-949C-4B0B-9D43-F42D92077E6F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A06E824C-AC2D-4A85-8B36-510FA7268C0A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{242600EC-3DC6-4B18-B5AC-906E18FE43F7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8540028C-43BB-4B8C-A5E6-037B07A9AD60}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -3149,291 +3149,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA4CB56B-81C4-4C93-B38D-C479B7F1BA14}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A06E824C-AC2D-4A85-8B36-510FA7268C0A}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8540028C-43BB-4B8C-A5E6-037B07A9AD60}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -3149,4 +3149,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8A6F2E7-AE7D-4E03-8335-949876AB42B6}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14E4FF8F-9F3F-4646-AC71-F15E88C4B62F}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D81FC450-4323-4C90-86E2-9B9CF404E3F0}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -3149,291 +3149,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8A6F2E7-AE7D-4E03-8335-949876AB42B6}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14E4FF8F-9F3F-4646-AC71-F15E88C4B62F}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D81FC450-4323-4C90-86E2-9B9CF404E3F0}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -3149,4 +3149,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AFBC770-3257-4914-B56A-ED6E3BBC79B9}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C12CB516-A5F4-47C4-9878-6AA9044BDCD4}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{132081DA-B131-4F3B-9060-46EA033108D5}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -3427,13 +3427,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AFBC770-3257-4914-B56A-ED6E3BBC79B9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E17A8729-1769-4782-809A-40429E1FA68F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C12CB516-A5F4-47C4-9878-6AA9044BDCD4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18C8927C-D7A1-46C6-8601-06D8A3B143A5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{132081DA-B131-4F3B-9060-46EA033108D5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61C4F377-B95E-481D-A91C-552700E8E5B7}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -3427,13 +3427,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E17A8729-1769-4782-809A-40429E1FA68F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{258B57C6-864F-4E2E-8631-7111B8DBCC92}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18C8927C-D7A1-46C6-8601-06D8A3B143A5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{713B1B6C-39BA-4A33-B839-7E05D6485AE3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61C4F377-B95E-481D-A91C-552700E8E5B7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{709BA69F-A921-466F-808A-8B919B58A0D1}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -3427,13 +3427,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{258B57C6-864F-4E2E-8631-7111B8DBCC92}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D842690C-CF5B-4768-A512-985FEDD1F652}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{713B1B6C-39BA-4A33-B839-7E05D6485AE3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8808567C-49C8-4E2A-910B-32A54161585E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{709BA69F-A921-466F-808A-8B919B58A0D1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A17A4579-14D6-41C1-B535-C48624589089}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -3427,13 +3427,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D842690C-CF5B-4768-A512-985FEDD1F652}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6121D938-5638-4011-B7E7-83B9A2B274A8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8808567C-49C8-4E2A-910B-32A54161585E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1536B50D-1848-4341-AF16-025766795A96}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A17A4579-14D6-41C1-B535-C48624589089}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{691ED41A-C6C4-4076-888E-4B1228537F9D}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -3427,13 +3427,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6121D938-5638-4011-B7E7-83B9A2B274A8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80CF5250-E225-4136-89FF-B80905D26487}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1536B50D-1848-4341-AF16-025766795A96}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{166B66C7-B06C-4B16-A0FE-B0A55E7C3386}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{691ED41A-C6C4-4076-888E-4B1228537F9D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AC89608-D098-4FFF-818E-60D6F51BD8FB}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -3149,291 +3149,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80CF5250-E225-4136-89FF-B80905D26487}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{166B66C7-B06C-4B16-A0FE-B0A55E7C3386}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AC89608-D098-4FFF-818E-60D6F51BD8FB}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -3149,4 +3149,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0632E677-5AE0-47A7-9091-EBA07A74A97D}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{868CDEC1-A72D-4156-928A-3569F43091A0}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9712D5C2-D7AB-4DFC-A23E-2C62BB92A408}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -3427,13 +3427,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0632E677-5AE0-47A7-9091-EBA07A74A97D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{642F5FF3-1062-482D-ADF0-D351B039BBF8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{868CDEC1-A72D-4156-928A-3569F43091A0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C0338E1-2A00-439C-8FA2-534D5AC5F045}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9712D5C2-D7AB-4DFC-A23E-2C62BB92A408}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{124C0F00-8361-471C-982E-0CECCD7581C5}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -3427,13 +3427,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{642F5FF3-1062-482D-ADF0-D351B039BBF8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D875C8-5F57-4136-BB78-FEBE14D0F224}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C0338E1-2A00-439C-8FA2-534D5AC5F045}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AD84971-2EA0-4EC5-A0D2-16F76A5DDBFC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{124C0F00-8361-471C-982E-0CECCD7581C5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{725943CA-2261-4E2C-816E-FE72FEE0D318}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -3427,13 +3427,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D875C8-5F57-4136-BB78-FEBE14D0F224}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{232E9509-8215-47C4-8B02-A07803DDA8A0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AD84971-2EA0-4EC5-A0D2-16F76A5DDBFC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5254DC7-1090-4F2F-BAF9-F65F8A97FA6B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{725943CA-2261-4E2C-816E-FE72FEE0D318}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A60E5CEE-1E4A-4F12-9165-DB1A31056BDD}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -3427,13 +3427,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{232E9509-8215-47C4-8B02-A07803DDA8A0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD98FC16-660F-4D43-9295-0B24B942BB5C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5254DC7-1090-4F2F-BAF9-F65F8A97FA6B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{483B5DDB-E24E-497E-BF80-EAFA64E9D18D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A60E5CEE-1E4A-4F12-9165-DB1A31056BDD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB14482C-3FC8-46F1-AB85-338D8F5D41D2}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -3427,13 +3427,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD98FC16-660F-4D43-9295-0B24B942BB5C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7B88E02-DDAA-48E2-AD65-DC80D4672BE5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{483B5DDB-E24E-497E-BF80-EAFA64E9D18D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C10F8255-682D-41E7-92EC-77F845A10BF7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB14482C-3FC8-46F1-AB85-338D8F5D41D2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB8DCACD-D3B7-48E7-990C-6BC3CD7FE86D}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -3149,291 +3149,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7B88E02-DDAA-48E2-AD65-DC80D4672BE5}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C10F8255-682D-41E7-92EC-77F845A10BF7}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB8DCACD-D3B7-48E7-990C-6BC3CD7FE86D}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -3149,4 +3149,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{675AD2EA-D66C-4B3A-BB45-7D7A4E44A779}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6413F91-EB3B-447A-A516-0540F1EF5379}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22E9C73B-C1B2-49A6-9ECC-5C97C91BBFA5}"/>
 </file>